--- a/docs/harness/wirelist/RearFuel-wirelist.xlsx
+++ b/docs/harness/wirelist/RearFuel-wirelist.xlsx
@@ -1208,10 +1208,14 @@
       <c r="AB3" s="37" t="inlineStr"/>
       <c r="AC3" s="38" t="inlineStr"/>
       <c r="AD3" s="38" t="inlineStr"/>
-      <c r="AE3" s="38" t="inlineStr"/>
+      <c r="AE3" s="38" t="inlineStr">
+        <is>
+          <t>end t_trunk_fp_gnd: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_trunk_fp_gnd (Ground stud, trunk LH side (EWD ID TBD, M6 assumed)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG3" s="38" t="inlineStr"/>

--- a/docs/harness/wirelist/RearFuel-wirelist.xlsx
+++ b/docs/harness/wirelist/RearFuel-wirelist.xlsx
@@ -1409,14 +1409,10 @@
       </c>
       <c r="V5" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W5" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W5" s="34" t="inlineStr"/>
       <c r="X5" s="34" t="inlineStr">
         <is>
           <t>Blue-Yellow-Blue</t>

--- a/docs/harness/wirelist/RearFuel-wirelist.xlsx
+++ b/docs/harness/wirelist/RearFuel-wirelist.xlsx
@@ -1727,7 +1727,7 @@
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>ix_fuel_r on B-cabin</t>
+          <t>ix_fuel_r on ECU-cabin</t>
         </is>
       </c>
       <c r="F3" s="33" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="E3" s="27" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E4" s="43" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F4" s="44" t="inlineStr">
